--- a/output/roomself_excel/1456.xlsx
+++ b/output/roomself_excel/1456.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,10 +476,10 @@
         <v>1736</v>
       </c>
       <c r="E2" t="n">
-        <v>502</v>
+        <v>287</v>
       </c>
       <c r="F2" t="n">
-        <v>287</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>316464</v>
+        <v>121546</v>
       </c>
       <c r="D3" t="n">
-        <v>6348</v>
+        <v>3172</v>
       </c>
       <c r="E3" t="n">
-        <v>814</v>
+        <v>556</v>
       </c>
       <c r="F3" t="n">
-        <v>656</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>62545</v>
+        <v>54288</v>
       </c>
       <c r="D5" t="n">
-        <v>2012</v>
+        <v>1864</v>
       </c>
       <c r="E5" t="n">
-        <v>287</v>
+        <v>234</v>
       </c>
       <c r="F5" t="n">
-        <v>282</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>54288</v>
+        <v>62545</v>
       </c>
       <c r="D6" t="n">
-        <v>1864</v>
+        <v>2012</v>
       </c>
       <c r="E6" t="n">
-        <v>234</v>
+        <v>287</v>
       </c>
       <c r="F6" t="n">
-        <v>11</v>
+        <v>282</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>194918</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3944</v>
+      </c>
+      <c r="E7" t="n">
+        <v>814</v>
+      </c>
+      <c r="F7" t="n">
+        <v>656</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/1456.xlsx
+++ b/output/roomself_excel/1456.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,62 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
         </is>
       </c>
     </row>
@@ -475,12 +525,34 @@
       <c r="D2" t="n">
         <v>1736</v>
       </c>
-      <c r="E2" t="n">
-        <v>287</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>208</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="G2" t="n">
+        <v>11</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>197</v>
+      </c>
+      <c r="J2" t="n">
+        <v>12</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +569,42 @@
       <c r="D3" t="n">
         <v>3172</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>556</v>
       </c>
-      <c r="F3" t="n">
-        <v>249</v>
-      </c>
+      <c r="G3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>48</v>
+      </c>
+      <c r="J3" t="n">
+        <v>14</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>46</v>
+      </c>
+      <c r="M3" t="n">
+        <v>17</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +621,34 @@
       <c r="D4" t="n">
         <v>1868</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>234</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>11</v>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>233</v>
+      </c>
+      <c r="J4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +665,34 @@
       <c r="D5" t="n">
         <v>1864</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>232</v>
+      </c>
+      <c r="G5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>234</v>
       </c>
-      <c r="F5" t="n">
+      <c r="J5" t="n">
         <v>11</v>
       </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +709,34 @@
       <c r="D6" t="n">
         <v>2012</v>
       </c>
-      <c r="E6" t="n">
-        <v>287</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>282</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>229</v>
+      </c>
+      <c r="J6" t="n">
+        <v>9</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,11 +753,49 @@
       <c r="D7" t="n">
         <v>3944</v>
       </c>
-      <c r="E7" t="n">
-        <v>814</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>656</v>
+        <v>157</v>
+      </c>
+      <c r="G7" t="n">
+        <v>11</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>158</v>
+      </c>
+      <c r="J7" t="n">
+        <v>11</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>154</v>
+      </c>
+      <c r="M7" t="n">
+        <v>9</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>390</v>
+      </c>
+      <c r="P7" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
